--- a/data/trans_dic/IP19C02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por limpieza de boca</t>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,68</t>
+          <t>0,0; 79,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 63,86</t>
+          <t>7,92; 66,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 74,76</t>
+          <t>11,18; 74,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,11</t>
+          <t>0,0; 65,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 57,8</t>
+          <t>15,21; 60,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,63</t>
+          <t>1,07; 7,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,2</t>
+          <t>0,9; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 19,41</t>
+          <t>6,64; 18,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,06; 30,15</t>
+          <t>13,46; 29,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,26</t>
+          <t>0,84; 7,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 9,46</t>
+          <t>1,34; 9,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,98</t>
+          <t>5,88; 16,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,35; 46,81</t>
+          <t>26,77; 46,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,42</t>
+          <t>1,66; 6,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,85</t>
+          <t>1,74; 6,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 15,78</t>
+          <t>7,34; 15,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 36,2</t>
+          <t>22,55; 35,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,23</t>
+          <t>3,78; 12,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,54</t>
+          <t>1,63; 7,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 23,53</t>
+          <t>13,39; 23,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,59; 38,47</t>
+          <t>23,42; 38,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,3</t>
+          <t>4,49; 13,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 10,08</t>
+          <t>2,89; 9,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 24,07</t>
+          <t>13,06; 23,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,25; 27,71</t>
+          <t>16,64; 28,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,24</t>
+          <t>5,21; 11,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,18</t>
+          <t>2,8; 7,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 22,19</t>
+          <t>14,44; 21,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 30,14</t>
+          <t>21,28; 30,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 13,87</t>
+          <t>6,18; 13,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,89</t>
+          <t>5,22; 12,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 29,47</t>
+          <t>18,01; 29,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,91; 38,15</t>
+          <t>27,05; 38,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,17</t>
+          <t>4,66; 11,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,81</t>
+          <t>5,29; 12,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 33,69</t>
+          <t>21,19; 33,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 43,75</t>
+          <t>29,62; 43,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,87</t>
+          <t>6,32; 10,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,52</t>
+          <t>6,3; 12,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,15; 29,6</t>
+          <t>20,66; 29,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 39,5</t>
+          <t>29,77; 39,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,96</t>
+          <t>5,2; 9,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,09</t>
+          <t>3,9; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,53</t>
+          <t>15,74; 22,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,58; 33,85</t>
+          <t>25,63; 34,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,18</t>
+          <t>4,89; 9,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,85</t>
+          <t>4,61; 8,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,92; 23,03</t>
+          <t>16,14; 23,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,22; 35,7</t>
+          <t>27,38; 35,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,89</t>
+          <t>5,53; 8,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,74</t>
+          <t>4,76; 7,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,65</t>
+          <t>16,97; 21,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,74; 33,94</t>
+          <t>27,7; 33,7</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3782</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2609</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>459; 3879</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>594; 3974</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2594</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1691; 6721</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2578</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13705</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>27744</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5433</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16547</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>41450</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>906; 6669</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>691; 6577</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4517; 12798</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8908; 19481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>675; 5696</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1236; 8939</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4831; 13861</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>20646; 35675</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2729; 10152</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2936; 11391</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>11027; 23241</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>32316; 51241</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7256</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4474</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26921</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36837</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8706</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7674</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26956</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>35917</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15962</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12149</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>53877</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>72754</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3751; 11986</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2037; 9680</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19937; 35160</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28551; 46519</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4745; 14084</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3817; 13011</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19505; 35627</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>27415; 47336</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10680; 23625</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7196; 19240</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>43054; 65066</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>61001; 87331</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15546</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12682</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33797</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>63949</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12083</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>86914</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28487</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24765</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70293</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>150864</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10109; 22693</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7725; 18847</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26134; 42423</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>53497; 76686</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8090; 19236</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7474; 17806</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>28664; 45517</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>70257; 102158</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>21299; 37071</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18225; 34757</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>57913; 81691</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>129501; 169810</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25741</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20361</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>116339</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>152510</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>49882</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>43572</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>140716</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>268849</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>18261; 33783</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13779; 28946</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57080; 82128</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>100387; 133507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17678; 32695</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16876; 32379</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>59392; 85650</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>132619; 173719</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>39392; 61615</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>34252; 56189</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>123958; 159082</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>242682; 295243</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Edad-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,1</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 66,92</t>
+          <t>9,74; 71,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 74,76</t>
+          <t>11,43; 75,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,4</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 60,48</t>
+          <t>14,4; 56,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,91</t>
+          <t>1,27; 7,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,55</t>
+          <t>0,87; 8,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 18,8</t>
+          <t>6,64; 19,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 29,43</t>
+          <t>13,6; 29,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,08</t>
+          <t>0,84; 7,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 9,71</t>
+          <t>0,82; 8,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 16,88</t>
+          <t>5,88; 17,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,77; 46,25</t>
+          <t>26,68; 46,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,16</t>
+          <t>1,68; 6,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,74</t>
+          <t>1,59; 6,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,47</t>
+          <t>7,35; 15,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,55; 35,75</t>
+          <t>22,98; 36,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,08</t>
+          <t>3,91; 12,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,74</t>
+          <t>1,27; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 23,61</t>
+          <t>13,15; 23,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,42; 38,16</t>
+          <t>22,78; 36,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,32</t>
+          <t>4,62; 13,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,85</t>
+          <t>3,04; 10,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 23,86</t>
+          <t>12,98; 23,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 28,73</t>
+          <t>16,26; 27,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,53</t>
+          <t>4,87; 10,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,48</t>
+          <t>2,89; 7,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 21,82</t>
+          <t>14,23; 22,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 30,46</t>
+          <t>20,9; 30,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 13,88</t>
+          <t>6,17; 13,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,74</t>
+          <t>5,18; 13,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 29,24</t>
+          <t>17,98; 29,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,05; 38,78</t>
+          <t>27,1; 38,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,07</t>
+          <t>4,83; 11,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,61</t>
+          <t>5,35; 12,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 33,65</t>
+          <t>19,93; 33,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,62; 43,07</t>
+          <t>29,63; 43,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,99</t>
+          <t>6,11; 11,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,02</t>
+          <t>6,12; 11,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,66; 29,14</t>
+          <t>20,45; 29,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,77; 39,04</t>
+          <t>29,92; 39,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,63</t>
+          <t>5,27; 9,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,19</t>
+          <t>3,92; 7,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,74; 22,65</t>
+          <t>15,68; 22,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,63; 34,09</t>
+          <t>25,56; 33,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,04</t>
+          <t>4,79; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,85</t>
+          <t>4,56; 8,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 23,27</t>
+          <t>16,33; 23,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,86</t>
+          <t>27,2; 35,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,65</t>
+          <t>5,59; 8,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,81</t>
+          <t>4,8; 7,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,77</t>
+          <t>17,07; 21,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,7; 33,7</t>
+          <t>27,75; 33,78</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2609</t>
+          <t>0; 2638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>459; 3879</t>
+          <t>565; 4134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>594; 3974</t>
+          <t>607; 3990</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2594</t>
+          <t>0; 2649</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1691; 6721</t>
+          <t>1600; 6310</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>906; 6669</t>
+          <t>1069; 6691</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>691; 6577</t>
+          <t>670; 6396</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4517; 12798</t>
+          <t>4520; 13099</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8908; 19481</t>
+          <t>9002; 19855</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>675; 5696</t>
+          <t>679; 5913</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1236; 8939</t>
+          <t>755; 8117</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4831; 13861</t>
+          <t>4830; 14160</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20646; 35675</t>
+          <t>20579; 35930</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2729; 10152</t>
+          <t>2773; 9970</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2936; 11391</t>
+          <t>2686; 11186</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11027; 23241</t>
+          <t>11033; 23431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32316; 51241</t>
+          <t>32935; 51949</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3751; 11986</t>
+          <t>3877; 12594</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2037; 9680</t>
+          <t>1588; 9254</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19937; 35160</t>
+          <t>19585; 35346</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28551; 46519</t>
+          <t>27771; 45016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4745; 14084</t>
+          <t>4884; 14315</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3817; 13011</t>
+          <t>4012; 13214</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19505; 35627</t>
+          <t>19383; 35244</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27415; 47336</t>
+          <t>26795; 46010</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10680; 23625</t>
+          <t>9972; 22509</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7196; 19240</t>
+          <t>7425; 18727</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43054; 65066</t>
+          <t>42427; 65667</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61001; 87331</t>
+          <t>59928; 87090</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10109; 22693</t>
+          <t>10092; 22820</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7725; 18847</t>
+          <t>7660; 19391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26134; 42423</t>
+          <t>26084; 42515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53497; 76686</t>
+          <t>53592; 76934</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8090; 19236</t>
+          <t>8387; 19890</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7474; 17806</t>
+          <t>7560; 18161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28664; 45517</t>
+          <t>26958; 45795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70257; 102158</t>
+          <t>70292; 102769</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21299; 37071</t>
+          <t>20596; 37633</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18225; 34757</t>
+          <t>17680; 32752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57913; 81691</t>
+          <t>57347; 82099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>129501; 169810</t>
+          <t>130135; 170622</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18261; 33783</t>
+          <t>18506; 34662</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13779; 28946</t>
+          <t>13830; 27968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57080; 82128</t>
+          <t>56846; 81368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100387; 133507</t>
+          <t>100101; 131230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17678; 32695</t>
+          <t>17312; 32665</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16876; 32379</t>
+          <t>16690; 31697</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59392; 85650</t>
+          <t>60081; 86057</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>132619; 173719</t>
+          <t>131763; 173549</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39392; 61615</t>
+          <t>39819; 60805</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34252; 56189</t>
+          <t>34508; 53864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123958; 159082</t>
+          <t>124700; 158533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>242682; 295243</t>
+          <t>243120; 295973</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,57 +654,57 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36,32%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>31,71%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36,39%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 71,31</t>
+          <t>10,66; 75,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 76,68</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7,66; 64,67</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11,43; 75,06</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 66,11</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 66,77</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 56,78</t>
+          <t>16,05; 57,51</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,93</t>
+          <t>0,85; 7,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,31</t>
+          <t>1,34; 9,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 19,25</t>
+          <t>5,61; 16,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 29,99</t>
+          <t>26,79; 46,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,35</t>
+          <t>1,09; 7,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,82</t>
+          <t>0,88; 8,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 17,24</t>
+          <t>6,47; 19,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,68; 46,58</t>
+          <t>13,74; 30,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,05</t>
+          <t>1,6; 6,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,62</t>
+          <t>1,59; 6,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,6</t>
+          <t>7,31; 15,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,98; 36,24</t>
+          <t>22,61; 36,22</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,08%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 12,7</t>
+          <t>4,68; 13,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,4</t>
+          <t>3,04; 10,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,15; 23,74</t>
+          <t>13,3; 24,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,78; 36,93</t>
+          <t>18,14; 30,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,54</t>
+          <t>3,8; 12,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 10,0</t>
+          <t>1,33; 7,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 23,6</t>
+          <t>13,3; 23,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,26; 27,92</t>
+          <t>25,77; 40,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 10,98</t>
+          <t>5,24; 11,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,28</t>
+          <t>2,75; 7,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,23; 22,02</t>
+          <t>14,57; 22,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,9; 30,38</t>
+          <t>23,48; 32,91</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39,21%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>23,29%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,96</t>
+          <t>4,77; 11,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,11</t>
+          <t>5,3; 12,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 29,3</t>
+          <t>20,74; 33,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,1; 38,91</t>
+          <t>32,04; 46,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,45</t>
+          <t>6,34; 13,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 12,86</t>
+          <t>5,16; 12,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,93; 33,86</t>
+          <t>18,24; 29,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,63; 43,32</t>
+          <t>27,11; 39,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,16</t>
+          <t>6,15; 10,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,33</t>
+          <t>6,19; 11,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 29,28</t>
+          <t>21,15; 29,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,92; 39,23</t>
+          <t>32,09; 41,56</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,88</t>
+          <t>4,79; 9,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,92</t>
+          <t>4,56; 8,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,44</t>
+          <t>15,92; 23,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,56; 33,51</t>
+          <t>29,28; 37,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,03</t>
+          <t>5,47; 9,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,66</t>
+          <t>4,02; 8,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,38</t>
+          <t>15,77; 22,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,2; 35,82</t>
+          <t>26,78; 35,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,53</t>
+          <t>5,61; 8,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,49</t>
+          <t>4,69; 7,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 21,7</t>
+          <t>16,83; 21,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,75; 33,78</t>
+          <t>29,68; 35,79</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1582,57 +1582,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1847</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3624</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>565; 4134</t>
+          <t>498; 3545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0; 2529</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>465; 3927</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>607; 3990</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2622</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2649</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1600; 6310</t>
+          <t>1725; 6182</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24292</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2940</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2578</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8060</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13705</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2494</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3454</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8486</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>38137</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1069; 6691</t>
+          <t>683; 5842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>670; 6396</t>
+          <t>1229; 8714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4520; 13099</t>
+          <t>4610; 13948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9002; 19855</t>
+          <t>18099; 31667</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>679; 5913</t>
+          <t>919; 6434</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>755; 8117</t>
+          <t>674; 6308</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4830; 14160</t>
+          <t>4406; 13211</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20579; 35930</t>
+          <t>8719; 19655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2773; 9970</t>
+          <t>2639; 10572</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2686; 11186</t>
+          <t>2695; 11575</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11033; 23431</t>
+          <t>10973; 23693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32935; 51949</t>
+          <t>29625; 47453</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8706</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7674</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26956</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37879</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7256</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4474</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>26921</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36837</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8706</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7674</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26956</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72754</t>
+          <t>77466</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3877; 12594</t>
+          <t>4946; 14064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1588; 9254</t>
+          <t>4022; 13319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19585; 35346</t>
+          <t>19861; 35952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27771; 45016</t>
+          <t>28167; 48106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4884; 14315</t>
+          <t>3769; 12135</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4012; 13214</t>
+          <t>1665; 9432</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19383; 35244</t>
+          <t>19799; 35039</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26795; 46010</t>
+          <t>31402; 49045</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9972; 22509</t>
+          <t>10742; 23031</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7425; 18727</t>
+          <t>7061; 18472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42427; 65667</t>
+          <t>43452; 66187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59928; 87090</t>
+          <t>65084; 91201</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12083</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91578</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15546</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>12682</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>33797</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63949</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12942</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12083</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36496</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>86914</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>150864</t>
+          <t>160477</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10092; 22820</t>
+          <t>8287; 19398</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7660; 19391</t>
+          <t>7487; 18089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26084; 42515</t>
+          <t>28059; 45563</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53592; 76934</t>
+          <t>74823; 108862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8387; 19890</t>
+          <t>10372; 22676</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7560; 18161</t>
+          <t>7627; 19066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26958; 45795</t>
+          <t>26474; 42764</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70292; 102769</t>
+          <t>55547; 80604</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20596; 37633</t>
+          <t>20742; 36643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17680; 32752</t>
+          <t>17907; 33306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57347; 82099</t>
+          <t>59305; 82989</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>130135; 170622</t>
+          <t>140709; 182210</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18506; 34662</t>
+          <t>17335; 33220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13830; 27968</t>
+          <t>16688; 32387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56846; 81368</t>
+          <t>58586; 84759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100101; 131230</t>
+          <t>135027; 174902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17312; 32665</t>
+          <t>19209; 34955</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16690; 31697</t>
+          <t>14207; 28582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60081; 86057</t>
+          <t>57202; 81714</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131763; 173549</t>
+          <t>106109; 139724</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39819; 60805</t>
+          <t>39954; 63354</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34508; 53864</t>
+          <t>33764; 55641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124700; 158533</t>
+          <t>122953; 158157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>243120; 295973</t>
+          <t>254485; 306859</t>
         </is>
       </c>
     </row>
